--- a/FPSDemo/MiniTemplate/Datas/#pickup_item.xlsx
+++ b/FPSDemo/MiniTemplate/Datas/#pickup_item.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pickup_item" sheetId="1" r:id="R3d3978ba62b64f4d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pickup_item" sheetId="1" r:id="R39a01c0eb3844a1f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -878,7 +878,7 @@
         </x:is>
       </x:c>
       <x:c r="H8" s="3" t="n">
-        <x:v>55</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="I8" s="3" t="n">
         <x:v>2</x:v>
